--- a/Parametrit/Astuotanto/Asuntotuotanto_parametrit.xlsx
+++ b/Parametrit/Astuotanto/Asuntotuotanto_parametrit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanga\Documents\Vaestoennuste-main\Parametrit\Astuotanto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5380C35B-7421-4125-ABD8-1A0539236E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6592A7-38F8-4172-BFFB-8CFD23DC97F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{5FAAF97F-CDCB-4ACE-8511-B671FF06F9BA}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FAAF97F-CDCB-4ACE-8511-B671FF06F9BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Taul1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>muuttotyyp</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>hedtyyp</t>
   </si>
@@ -109,6 +106,15 @@
   </si>
   <si>
     <t>Kerrostalo</t>
+  </si>
+  <si>
+    <t>Kaupunkipientalo</t>
+  </si>
+  <si>
+    <t>Hoivakoti</t>
+  </si>
+  <si>
+    <t>OK-talo-haja-asutus</t>
   </si>
 </sst>
 </file>
@@ -154,10 +160,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -474,346 +478,512 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9128BBEF-8E77-4B85-9833-C424E24BB353}">
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.1796875" style="1" customWidth="1"/>
-    <col min="2" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.54296875" style="1" customWidth="1"/>
-    <col min="6" max="9" width="8" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" style="1" customWidth="1"/>
-    <col min="11" max="23" width="8.7265625" style="1"/>
-    <col min="24" max="24" width="18.81640625" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.7265625" style="1"/>
+    <col min="2" max="8" width="8" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.453125" style="1" customWidth="1"/>
+    <col min="10" max="22" width="8.7265625" style="1"/>
+    <col min="23" max="23" width="18.81640625" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>42.7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1</v>
+      </c>
+      <c r="T2" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="D3" s="1">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1">
+        <v>10</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>10</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1">
+        <v>10</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>50</v>
+      </c>
+      <c r="S3" s="1">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>42.3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>10</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>10</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>10</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>50</v>
+      </c>
+      <c r="S4" s="1">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="D5" s="1">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>10</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>10</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>10</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>50</v>
+      </c>
+      <c r="S5" s="1">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>42.7</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>10</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1">
+        <v>50</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>58</v>
+      </c>
+      <c r="D7" s="1">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1">
         <v>5</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>45</v>
-      </c>
-      <c r="D2" s="3">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3">
-        <v>10</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3">
-        <v>10</v>
-      </c>
-      <c r="N2" s="3">
-        <v>1</v>
-      </c>
-      <c r="O2" s="3">
-        <v>10</v>
-      </c>
-      <c r="P2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>10</v>
-      </c>
-      <c r="R2" s="3">
-        <v>1</v>
-      </c>
-      <c r="S2" s="3">
-        <v>50</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4">
-        <v>43</v>
-      </c>
-      <c r="D3" s="3">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3">
-        <v>4</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>10</v>
-      </c>
-      <c r="L3" s="3">
-        <v>1</v>
-      </c>
-      <c r="M3" s="3">
-        <v>10</v>
-      </c>
-      <c r="N3" s="3">
-        <v>1</v>
-      </c>
-      <c r="O3" s="3">
-        <v>10</v>
-      </c>
-      <c r="P3" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>10</v>
-      </c>
-      <c r="R3" s="3">
-        <v>1</v>
-      </c>
-      <c r="S3" s="3">
-        <v>50</v>
-      </c>
-      <c r="T3" s="3">
-        <v>1</v>
-      </c>
-      <c r="U3" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="3">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4">
-        <v>42</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3">
-        <v>4</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>10</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" s="3">
-        <v>10</v>
-      </c>
-      <c r="N4" s="3">
-        <v>1</v>
-      </c>
-      <c r="O4" s="3">
-        <v>10</v>
-      </c>
-      <c r="P4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>10</v>
-      </c>
-      <c r="R4" s="3">
-        <v>1</v>
-      </c>
-      <c r="S4" s="3">
-        <v>50</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="3">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4">
-        <v>39.5</v>
-      </c>
-      <c r="D5" s="3">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3">
-        <v>1</v>
-      </c>
-      <c r="M5" s="3">
-        <v>10</v>
-      </c>
-      <c r="N5" s="3">
-        <v>1</v>
-      </c>
-      <c r="O5" s="3">
-        <v>10</v>
-      </c>
-      <c r="P5" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>10</v>
-      </c>
-      <c r="R5" s="3">
-        <v>1</v>
-      </c>
-      <c r="S5" s="3">
-        <v>50</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C6" s="2"/>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>10</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>10</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1">
+        <v>50</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
